--- a/app/analytical-backend/data/08_reporting/results.xlsx
+++ b/app/analytical-backend/data/08_reporting/results.xlsx
@@ -81,7 +81,7 @@
     <t>Chained $, Billions</t>
   </si>
   <si>
-    <t>17/06/2025 11:16</t>
+    <t>05/07/2025 13:38</t>
   </si>
   <si>
     <t>15/10/2024 00:00</t>
@@ -702,13 +702,13 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>15911.45000807181</v>
+        <v>15911.45000806028</v>
       </c>
       <c r="C2">
-        <v>0.002592894152714171</v>
+        <v>0.002592894151987621</v>
       </c>
       <c r="D2">
-        <v>399.8906796358289</v>
+        <v>399.8906798500913</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -730,7 +730,7 @@
         <v>6</v>
       </c>
       <c r="B4">
-        <v>157.4588329235442</v>
+        <v>157.4588329235457</v>
       </c>
       <c r="C4">
         <v>0.00227380010461742</v>
@@ -852,7 +852,7 @@
         <v>44958</v>
       </c>
       <c r="B2">
-        <v>15279.23738761561</v>
+        <v>15279.2373876156</v>
       </c>
       <c r="C2">
         <v>15325.5</v>
@@ -907,7 +907,7 @@
         <v>45108</v>
       </c>
       <c r="B7">
-        <v>15434.91718733836</v>
+        <v>15434.91718733837</v>
       </c>
       <c r="C7">
         <v>15448.3</v>
@@ -951,7 +951,7 @@
         <v>45231</v>
       </c>
       <c r="B11">
-        <v>15583.98581120782</v>
+        <v>15583.98581120781</v>
       </c>
       <c r="C11">
         <v>15584.29999999999</v>
@@ -1039,7 +1039,7 @@
         <v>45474</v>
       </c>
       <c r="B19">
-        <v>15872.88007831158</v>
+        <v>15872.88007831159</v>
       </c>
       <c r="C19">
         <v>15870.29999999999</v>
@@ -1144,7 +1144,7 @@
         <v>71</v>
       </c>
       <c r="D6">
-        <v>7.888509312517782</v>
+        <v>7.881718243879401</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1158,7 +1158,7 @@
         <v>72</v>
       </c>
       <c r="D7">
-        <v>-17.82203720781681</v>
+        <v>-17.67398884695215</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1186,7 +1186,7 @@
         <v>74</v>
       </c>
       <c r="D9">
-        <v>-3.930898927383719</v>
+        <v>-4.147879946871359</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1200,7 +1200,7 @@
         <v>75</v>
       </c>
       <c r="D10">
-        <v>82.15955977060796</v>
+        <v>82.66932246950591</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1256,7 +1256,7 @@
         <v>79</v>
       </c>
       <c r="D14">
-        <v>-3.457477548094389</v>
+        <v>-3.54597675197193</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1284,7 +1284,7 @@
         <v>81</v>
       </c>
       <c r="D16">
-        <v>-1.912014929421387</v>
+        <v>-1.844353622662937</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1312,7 +1312,7 @@
         <v>83</v>
       </c>
       <c r="D18">
-        <v>6.666950103081809</v>
+        <v>6.691586215363866</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1354,7 +1354,7 @@
         <v>86</v>
       </c>
       <c r="D21">
-        <v>-1.697613261252926</v>
+        <v>-1.699986866034498</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1368,7 +1368,7 @@
         <v>87</v>
       </c>
       <c r="D22">
-        <v>-63.39390418002188</v>
+        <v>-63.88445680377235</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1424,7 +1424,7 @@
         <v>91</v>
       </c>
       <c r="D26">
-        <v>-6.656509990085508</v>
+        <v>-6.601420948353007</v>
       </c>
     </row>
   </sheetData>
@@ -5194,7 +5194,7 @@
         <v>97</v>
       </c>
       <c r="B3">
-        <v>0.0009867029955283868</v>
+        <v>0.0009867029955283994</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -5202,7 +5202,7 @@
         <v>98</v>
       </c>
       <c r="B4">
-        <v>288</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" spans="1:2">

--- a/app/analytical-backend/data/08_reporting/results.xlsx
+++ b/app/analytical-backend/data/08_reporting/results.xlsx
@@ -81,7 +81,7 @@
     <t>Chained $, Billions</t>
   </si>
   <si>
-    <t>17/06/2025 11:16</t>
+    <t>24/07/2025 14:34</t>
   </si>
   <si>
     <t>15/10/2024 00:00</t>
@@ -702,13 +702,13 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>15911.45000807181</v>
+        <v>15911.45000806028</v>
       </c>
       <c r="C2">
-        <v>0.002592894152714171</v>
+        <v>0.002592894151987621</v>
       </c>
       <c r="D2">
-        <v>399.8906796358289</v>
+        <v>399.8906750727404</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -730,7 +730,7 @@
         <v>6</v>
       </c>
       <c r="B4">
-        <v>157.4588329235442</v>
+        <v>157.4588329235457</v>
       </c>
       <c r="C4">
         <v>0.00227380010461742</v>
@@ -852,7 +852,7 @@
         <v>44958</v>
       </c>
       <c r="B2">
-        <v>15279.23738761561</v>
+        <v>15279.2373876156</v>
       </c>
       <c r="C2">
         <v>15325.5</v>
@@ -907,7 +907,7 @@
         <v>45108</v>
       </c>
       <c r="B7">
-        <v>15434.91718733836</v>
+        <v>15434.91718733837</v>
       </c>
       <c r="C7">
         <v>15448.3</v>
@@ -951,7 +951,7 @@
         <v>45231</v>
       </c>
       <c r="B11">
-        <v>15583.98581120782</v>
+        <v>15583.98581120781</v>
       </c>
       <c r="C11">
         <v>15584.29999999999</v>
@@ -1039,7 +1039,7 @@
         <v>45474</v>
       </c>
       <c r="B19">
-        <v>15872.88007831158</v>
+        <v>15872.88007831159</v>
       </c>
       <c r="C19">
         <v>15870.29999999999</v>
@@ -1144,7 +1144,7 @@
         <v>71</v>
       </c>
       <c r="D6">
-        <v>7.888509312517782</v>
+        <v>8.334359592366615</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1158,7 +1158,7 @@
         <v>72</v>
       </c>
       <c r="D7">
-        <v>-17.82203720781681</v>
+        <v>-17.99198573196398</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1186,7 +1186,7 @@
         <v>74</v>
       </c>
       <c r="D9">
-        <v>-3.930898927383719</v>
+        <v>-4.1897062203851</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1200,7 +1200,7 @@
         <v>75</v>
       </c>
       <c r="D10">
-        <v>82.15955977060796</v>
+        <v>82.12388342047079</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1256,7 +1256,7 @@
         <v>79</v>
       </c>
       <c r="D14">
-        <v>-3.457477548094389</v>
+        <v>-3.32071070501111</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1284,7 +1284,7 @@
         <v>81</v>
       </c>
       <c r="D16">
-        <v>-1.912014929421387</v>
+        <v>-2.096896500353291</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1312,7 +1312,7 @@
         <v>83</v>
       </c>
       <c r="D18">
-        <v>6.666950103081809</v>
+        <v>6.561942539127226</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1354,7 +1354,7 @@
         <v>86</v>
       </c>
       <c r="D21">
-        <v>-1.697613261252926</v>
+        <v>-1.491573662978029</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1368,7 +1368,7 @@
         <v>87</v>
       </c>
       <c r="D22">
-        <v>-63.39390418002188</v>
+        <v>-63.71891301086018</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1424,7 +1424,7 @@
         <v>91</v>
       </c>
       <c r="D26">
-        <v>-6.656509990085508</v>
+        <v>-6.365836578281993</v>
       </c>
     </row>
   </sheetData>
@@ -5194,7 +5194,7 @@
         <v>97</v>
       </c>
       <c r="B3">
-        <v>0.0009867029955283868</v>
+        <v>0.0009867029955283994</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -5202,7 +5202,7 @@
         <v>98</v>
       </c>
       <c r="B4">
-        <v>288</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" spans="1:2">
